--- a/data/trans_orig/P17E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22789</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>40415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34682</t>
+          <t>35100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69652</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>39893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55961</t>
+          <t>57458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84611</t>
+          <t>82939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>107732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61937</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80683</t>
+          <t>80205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110074</t>
+          <t>109712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131765</t>
+          <t>132439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32549</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84781</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101828</t>
+          <t>101352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148901</t>
+          <t>147606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54326</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57415</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>69693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103120</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234951</t>
+          <t>236000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259420</t>
+          <t>258979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165055</t>
+          <t>164715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188508</t>
+          <t>188793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408627</t>
+          <t>409477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442317</t>
+          <t>442054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63838</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74556</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151500</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174335</t>
+          <t>175237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218422</t>
+          <t>218515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244968</t>
+          <t>244642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50705</t>
+          <t>49665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>77996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>55963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87987</t>
+          <t>87582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21461</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314215</t>
+          <t>315932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>343223</t>
+          <t>344263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>331002</t>
+          <t>331407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>362547</t>
+          <t>363026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110330</t>
+          <t>109455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152269</t>
+          <t>150642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182290</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>238596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308821</t>
+          <t>309766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>372734</t>
+          <t>376849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>504110</t>
+          <t>505737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>546049</t>
+          <t>546924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>809774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>866080</t>
+          <t>861914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332015</t>
+          <t>1327900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1395928</t>
+          <t>1394983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2012 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>45769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54217</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>68894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>53252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68856</t>
+          <t>69004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>110824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132447</t>
+          <t>132723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38950</t>
+          <t>39287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32816</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64889</t>
+          <t>62088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57071</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76964</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>64844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81298</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127927</t>
+          <t>130728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154520</t>
+          <t>156446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52292</t>
+          <t>53165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103983</t>
+          <t>103110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>125826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68429</t>
+          <t>68355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>83213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177971</t>
+          <t>177983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>206021</t>
+          <t>204977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>67623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68923</t>
+          <t>69395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87887</t>
+          <t>88010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>124977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235785</t>
+          <t>232911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262338</t>
+          <t>262396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180277</t>
+          <t>179805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206714</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>423646</t>
+          <t>424758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>461848</t>
+          <t>461725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25691</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>50320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>42982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70100</t>
+          <t>71056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82500</t>
+          <t>81657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97073</t>
+          <t>97097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230189</t>
+          <t>227871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250369</t>
+          <t>251038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316282</t>
+          <t>315326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344474</t>
+          <t>343400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>50682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80751</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>89981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275675</t>
+          <t>275216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305189</t>
+          <t>305744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305039</t>
+          <t>304810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335915</t>
+          <t>336188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136618</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185178</t>
+          <t>184968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188302</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239427</t>
+          <t>240075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338728</t>
+          <t>341218</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>410039</t>
+          <t>409705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592012</t>
+          <t>592222</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640572</t>
+          <t>640684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>912982</t>
+          <t>912334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>964107</t>
+          <t>966430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1519560</t>
+          <t>1519894</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1590871</t>
+          <t>1588381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>69118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87356</t>
+          <t>86635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>60985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78483</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136165</t>
+          <t>135993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161104</t>
+          <t>160718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53945</t>
+          <t>52871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65649</t>
+          <t>67381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>62387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79254</t>
+          <t>79708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134475</t>
+          <t>135549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158599</t>
+          <t>157537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>35802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47836</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118159</t>
+          <t>117038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136978</t>
+          <t>136740</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>57401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167844</t>
+          <t>168098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190836</t>
+          <t>190427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61957</t>
+          <t>61500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37003</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64824</t>
+          <t>65188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80419</t>
+          <t>79845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116967</t>
+          <t>118501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230327</t>
+          <t>230784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256228</t>
+          <t>256517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204480</t>
+          <t>204116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232301</t>
+          <t>230513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>444621</t>
+          <t>443087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481169</t>
+          <t>481743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26966</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47784</t>
+          <t>48114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69598</t>
+          <t>68368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118774</t>
+          <t>118444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>139886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205496</t>
+          <t>206145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232099</t>
+          <t>232358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331124</t>
+          <t>334417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365851</t>
+          <t>367081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47341</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78175</t>
+          <t>76718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84796</t>
+          <t>86904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>32555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>41890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289557</t>
+          <t>291014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320391</t>
+          <t>319666</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>327612</t>
+          <t>325504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357426</t>
+          <t>358339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>181224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195723</t>
+          <t>194441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251651</t>
+          <t>249051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343717</t>
+          <t>342850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>412053</t>
+          <t>414746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>672677</t>
+          <t>670410</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>718116</t>
+          <t>718216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>908631</t>
+          <t>911231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>964559</t>
+          <t>965841</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599862</t>
+          <t>1597169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1668198</t>
+          <t>1669065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48678</t>
+          <t>47302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>44245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61191</t>
+          <t>60942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86149</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71607</t>
+          <t>72983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92979</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63647</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141535</t>
+          <t>140633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>166742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>56203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61475</t>
+          <t>61073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>77013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>72847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124276</t>
+          <t>125226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>145905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62744</t>
+          <t>62338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75675</t>
+          <t>76217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>39176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>95079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112916</t>
+          <t>113507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>43796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70926</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34714</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85146</t>
+          <t>84716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>115810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146389</t>
+          <t>146447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173544</t>
+          <t>173519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135508</t>
+          <t>135939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155654</t>
+          <t>155548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289813</t>
+          <t>291872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322536</t>
+          <t>322966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63095</t>
+          <t>63392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>77199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207829</t>
+          <t>206576</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250720</t>
+          <t>250665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279022</t>
+          <t>278076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>324795</t>
+          <t>326214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>40228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49156</t>
+          <t>47784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131164</t>
+          <t>132171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150183</t>
+          <t>151346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146532</t>
+          <t>147904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169958</t>
+          <t>169898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131502</t>
+          <t>133712</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175131</t>
+          <t>178981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>142528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215686</t>
+          <t>214626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>292916</t>
+          <t>289104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>378284</t>
+          <t>376607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>450795</t>
+          <t>446945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>494424</t>
+          <t>492214</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661403</t>
+          <t>662463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>736289</t>
+          <t>734561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1124731</t>
+          <t>1126408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1210099</t>
+          <t>1213911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46531</t>
+          <t>46329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>55844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39893</t>
+          <t>40077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57458</t>
+          <t>56274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82939</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107732</t>
+          <t>107934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55387</t>
+          <t>55412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>61997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80205</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109712</t>
+          <t>109172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132439</t>
+          <t>131559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15089</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22311</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>13,62%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15089</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9299</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22749</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>83665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101352</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>44151</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>36929</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>51169</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>74,53%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>62,34%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>86,38%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>44151</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36491</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>61,6%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>140</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126266</t>
+          <t>127583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147606</t>
+          <t>149931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>52143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57755</t>
+          <t>58582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>68155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102270</t>
+          <t>101156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236000</t>
+          <t>237134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258979</t>
+          <t>259476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164715</t>
+          <t>163888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188793</t>
+          <t>187898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409477</t>
+          <t>410591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442054</t>
+          <t>443592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22632</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>74149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153826</t>
+          <t>153421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175237</t>
+          <t>175188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218515</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244642</t>
+          <t>245931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77996</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55963</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87582</t>
+          <t>86784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315932</t>
+          <t>314553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>343133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>331407</t>
+          <t>332205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>363026</t>
+          <t>362877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109455</t>
+          <t>109354</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150642</t>
+          <t>150916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>187574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238596</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309766</t>
+          <t>306069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376849</t>
+          <t>373533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505737</t>
+          <t>505463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>546924</t>
+          <t>547025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>809774</t>
+          <t>810720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1327900</t>
+          <t>1331216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1394983</t>
+          <t>1398680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25538</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23870</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>45227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>53158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>68555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53252</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>68296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>111366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>133053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39287</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>63797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56734</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76022</t>
+          <t>76840</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>64581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81382</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130728</t>
+          <t>129019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156446</t>
+          <t>154514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>53242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44304</t>
+          <t>43349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103110</t>
+          <t>103033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125826</t>
+          <t>126431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68355</t>
+          <t>67596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83213</t>
+          <t>82757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177983</t>
+          <t>178538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204977</t>
+          <t>205932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67623</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69395</t>
+          <t>68322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88010</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124977</t>
+          <t>125003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>232911</t>
+          <t>234855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262396</t>
+          <t>262444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179805</t>
+          <t>180878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206583</t>
+          <t>206963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424758</t>
+          <t>424732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>461725</t>
+          <t>462706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42982</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>68837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81657</t>
+          <t>82762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97097</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>227871</t>
+          <t>228048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251038</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315326</t>
+          <t>317545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343400</t>
+          <t>344123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50682</t>
+          <t>52782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81210</t>
+          <t>79473</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58603</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89981</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275216</t>
+          <t>276953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305744</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304810</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>336188</t>
+          <t>335698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136506</t>
+          <t>138611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184968</t>
+          <t>187907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185979</t>
+          <t>187389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>240075</t>
+          <t>239346</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>341218</t>
+          <t>336307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>409705</t>
+          <t>411720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592222</t>
+          <t>589283</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640684</t>
+          <t>638579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>912334</t>
+          <t>913063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>966430</t>
+          <t>965020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1519894</t>
+          <t>1517879</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1588381</t>
+          <t>1593292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69118</t>
+          <t>70039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86635</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60985</t>
+          <t>59932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78821</t>
+          <t>78197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135993</t>
+          <t>135358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160718</t>
+          <t>162216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30883</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>52544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67381</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>82743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62387</t>
+          <t>61766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79708</t>
+          <t>78739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135549</t>
+          <t>135876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157537</t>
+          <t>156887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>47527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117038</t>
+          <t>116107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136740</t>
+          <t>136745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168098</t>
+          <t>168153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190427</t>
+          <t>190199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61500</t>
+          <t>62971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79845</t>
+          <t>81835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118501</t>
+          <t>119675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230784</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256517</t>
+          <t>256424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204116</t>
+          <t>205035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>231687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443087</t>
+          <t>441913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481743</t>
+          <t>479753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62746</t>
+          <t>62190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>68909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101032</t>
+          <t>102921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118444</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139886</t>
+          <t>139718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206145</t>
+          <t>206701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232358</t>
+          <t>232243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334417</t>
+          <t>332528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367081</t>
+          <t>366540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>78912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54069</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86904</t>
+          <t>84345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>41835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>288820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>319666</t>
+          <t>320201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325504</t>
+          <t>328063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>358339</t>
+          <t>358267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133418</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181224</t>
+          <t>180688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194441</t>
+          <t>195282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249051</t>
+          <t>251053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342850</t>
+          <t>339964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>414746</t>
+          <t>415435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>670410</t>
+          <t>670946</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>718216</t>
+          <t>718290</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>911231</t>
+          <t>909229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>965841</t>
+          <t>965000</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1597169</t>
+          <t>1596480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1669065</t>
+          <t>1671951</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>53881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44245</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>72874</t>
+          <t>82307</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60942</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87051</t>
+          <t>97562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83062</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72983</t>
+          <t>77570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92743</t>
+          <t>99607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71748</t>
+          <t>79686</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63154</t>
+          <t>71425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80035</t>
+          <t>88396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>154810</t>
+          <t>169525</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140633</t>
+          <t>154270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166742</t>
+          <t>182323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>46556</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56203</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>75910</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>66422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77013</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>75032</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>67075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>136632</t>
+          <t>150941</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125226</t>
+          <t>140363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145905</t>
+          <t>161118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>45643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70476</t>
+          <t>78634</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62338</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76217</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39176</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>104798</t>
+          <t>116691</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95079</t>
+          <t>104989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113507</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>75208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>52965</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>64163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>99544</t>
+          <t>113578</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>98353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115810</t>
+          <t>133628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161134</t>
+          <t>170547</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146447</t>
+          <t>155952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173519</t>
+          <t>184164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>147005</t>
+          <t>163573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135939</t>
+          <t>152375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>173985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>308138</t>
+          <t>334120</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291872</t>
+          <t>314070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322966</t>
+          <t>349345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>407682</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>26800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41513</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62104</t>
+          <t>56704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57938</t>
+          <t>62713</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78210</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>75974</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63392</t>
+          <t>67685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77199</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>227167</t>
+          <t>173938</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206576</t>
+          <t>161436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250665</t>
+          <t>183569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>298348</t>
+          <t>249911</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278076</t>
+          <t>236008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326214</t>
+          <t>261886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>94485</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>94485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>94485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>356286</t>
+          <t>312624</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356286</t>
+          <t>312624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>356286</t>
+          <t>312624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>27760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47784</t>
+          <t>51184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>142546</t>
+          <t>162035</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132171</t>
+          <t>150659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151346</t>
+          <t>170952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>160187</t>
+          <t>178188</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147904</t>
+          <t>164921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169898</t>
+          <t>188345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>152785</t>
+          <t>166167</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133712</t>
+          <t>143621</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178981</t>
+          <t>190855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>187315</t>
+          <t>210846</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142528</t>
+          <t>187435</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214626</t>
+          <t>236545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>340101</t>
+          <t>377013</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289104</t>
+          <t>343377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376607</t>
+          <t>407962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473141</t>
+          <t>507057</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>446945</t>
+          <t>482369</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>492214</t>
+          <t>529603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>689774</t>
+          <t>692320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>662463</t>
+          <t>666621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>734561</t>
+          <t>715731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1162914</t>
+          <t>1199376</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1126408</t>
+          <t>1168427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1213911</t>
+          <t>1233012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>625926</t>
+          <t>673224</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>625926</t>
+          <t>673224</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>625926</t>
+          <t>673224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1503015</t>
+          <t>1576389</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1503015</t>
+          <t>1576389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1503015</t>
+          <t>1576389</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P17E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Clase-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10451,7 +10451,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
